--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/1.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/1.xlsx
@@ -426,13 +426,13 @@
         <v>-15.85366404146104</v>
       </c>
       <c r="E2">
-        <v>-11.74079549743423</v>
+        <v>-6.22741914936164</v>
       </c>
       <c r="F2">
-        <v>-1.589536973796467</v>
+        <v>-1.67027430136557</v>
       </c>
       <c r="G2">
-        <v>-11.26984303909379</v>
+        <v>-10.60259927510814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.74895465640504</v>
       </c>
       <c r="E3">
-        <v>-12.44089305054606</v>
+        <v>-7.397142099438923</v>
       </c>
       <c r="F3">
-        <v>-1.392425768149043</v>
+        <v>-1.400353799961733</v>
       </c>
       <c r="G3">
-        <v>-11.12306338151912</v>
+        <v>-10.19127392349032</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.59058453298722</v>
       </c>
       <c r="E4">
-        <v>-13.31981551374678</v>
+        <v>-8.926856090755964</v>
       </c>
       <c r="F4">
-        <v>-1.92964415396075</v>
+        <v>-1.727959205629537</v>
       </c>
       <c r="G4">
-        <v>-10.41788076565343</v>
+        <v>-9.285316652304441</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.36746276275407</v>
       </c>
       <c r="E5">
-        <v>-13.63015183749243</v>
+        <v>-9.695772863362359</v>
       </c>
       <c r="F5">
-        <v>-1.663880088731983</v>
+        <v>-1.437347586440483</v>
       </c>
       <c r="G5">
-        <v>-10.01043206286209</v>
+        <v>-9.513313923594049</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.07016378951671</v>
       </c>
       <c r="E6">
-        <v>-14.84751433413041</v>
+        <v>-11.3026520517701</v>
       </c>
       <c r="F6">
-        <v>-1.310668533970397</v>
+        <v>-1.42079785962414</v>
       </c>
       <c r="G6">
-        <v>-10.06778064323888</v>
+        <v>-8.218132502810521</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.70687161301907</v>
       </c>
       <c r="E7">
-        <v>-14.84815284896549</v>
+        <v>-9.428891776194314</v>
       </c>
       <c r="F7">
-        <v>-1.58652872441009</v>
+        <v>-1.338228976163832</v>
       </c>
       <c r="G7">
-        <v>-9.345902946218644</v>
+        <v>-10.15424878217911</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.2955719364273</v>
       </c>
       <c r="E8">
-        <v>-16.51183721532545</v>
+        <v>-11.22373433523843</v>
       </c>
       <c r="F8">
-        <v>-1.297629883168584</v>
+        <v>-1.267029517470463</v>
       </c>
       <c r="G8">
-        <v>-9.693321526746381</v>
+        <v>-8.985050171892546</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.86358306083792</v>
       </c>
       <c r="E9">
-        <v>-16.74841375443416</v>
+        <v>-11.4752186107804</v>
       </c>
       <c r="F9">
-        <v>-1.126482744151831</v>
+        <v>-0.9357174481075725</v>
       </c>
       <c r="G9">
-        <v>-9.784623062173941</v>
+        <v>-8.481618822281115</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.44533647847811</v>
       </c>
       <c r="E10">
-        <v>-17.95680081558894</v>
+        <v>-12.59331242869623</v>
       </c>
       <c r="F10">
-        <v>-1.039007539765491</v>
+        <v>-0.7214871733672052</v>
       </c>
       <c r="G10">
-        <v>-9.007359938281693</v>
+        <v>-8.117054926405494</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.07810942457358</v>
       </c>
       <c r="E11">
-        <v>-18.69528171438978</v>
+        <v>-12.96065771172444</v>
       </c>
       <c r="F11">
-        <v>-0.5720645202454934</v>
+        <v>-1.083234111160053</v>
       </c>
       <c r="G11">
-        <v>-8.470594705635342</v>
+        <v>-8.537212813522096</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.7957140987609</v>
       </c>
       <c r="E12">
-        <v>-19.21194889934692</v>
+        <v>-14.93792531769355</v>
       </c>
       <c r="F12">
-        <v>-0.91733774910594</v>
+        <v>-0.5882246554066375</v>
       </c>
       <c r="G12">
-        <v>-7.792455936279953</v>
+        <v>-7.531899449611615</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.6174746865365</v>
       </c>
       <c r="E13">
-        <v>-20.10635874365387</v>
+        <v>-15.02425614617578</v>
       </c>
       <c r="F13">
-        <v>-0.3910873186116083</v>
+        <v>-0.5310829622716668</v>
       </c>
       <c r="G13">
-        <v>-7.78992999003349</v>
+        <v>-7.046308629911317</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.55356951387016</v>
       </c>
       <c r="E14">
-        <v>-19.87080563967089</v>
+        <v>-14.82762074781471</v>
       </c>
       <c r="F14">
-        <v>-0.3576410333834426</v>
+        <v>-0.4803299387995789</v>
       </c>
       <c r="G14">
-        <v>-6.908113216919981</v>
+        <v>-6.811422113354487</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.58791871151558</v>
       </c>
       <c r="E15">
-        <v>-20.94940663576583</v>
+        <v>-17.10262646284013</v>
       </c>
       <c r="F15">
-        <v>0.01331357060177006</v>
+        <v>0.01494478769467269</v>
       </c>
       <c r="G15">
-        <v>-7.52510621016503</v>
+        <v>-6.406032569888573</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.68049541091328</v>
       </c>
       <c r="E16">
-        <v>-21.2125834311956</v>
+        <v>-16.95533331726665</v>
       </c>
       <c r="F16">
-        <v>0.5022059622568007</v>
+        <v>0.1624915411595465</v>
       </c>
       <c r="G16">
-        <v>-6.952914829702937</v>
+        <v>-5.606482853425953</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.77683609747179</v>
       </c>
       <c r="E17">
-        <v>-21.92572298944953</v>
+        <v>-18.3546363141108</v>
       </c>
       <c r="F17">
-        <v>0.4435027350892066</v>
+        <v>0.2143745388023006</v>
       </c>
       <c r="G17">
-        <v>-6.848963699769822</v>
+        <v>-5.349862605403808</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.82199045521831</v>
       </c>
       <c r="E18">
-        <v>-23.64025759044161</v>
+        <v>-18.57549451993889</v>
       </c>
       <c r="F18">
-        <v>0.5756043966137573</v>
+        <v>0.2829949324123764</v>
       </c>
       <c r="G18">
-        <v>-5.99141984655025</v>
+        <v>-5.756242001985964</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.77230434384863</v>
       </c>
       <c r="E19">
-        <v>-24.16898410168118</v>
+        <v>-20.27840452815328</v>
       </c>
       <c r="F19">
-        <v>1.026059453848115</v>
+        <v>0.9870686142099956</v>
       </c>
       <c r="G19">
-        <v>-6.259534308684745</v>
+        <v>-4.528996286213821</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.60136232876756</v>
       </c>
       <c r="E20">
-        <v>-25.2863035505417</v>
+        <v>-21.42268651125548</v>
       </c>
       <c r="F20">
-        <v>0.957187250997484</v>
+        <v>1.289049658165989</v>
       </c>
       <c r="G20">
-        <v>-5.62939182855771</v>
+        <v>-5.182517838939188</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.30934012026088</v>
       </c>
       <c r="E21">
-        <v>-25.43955616790928</v>
+        <v>-21.87950991220125</v>
       </c>
       <c r="F21">
-        <v>1.241167893518593</v>
+        <v>1.441558954116893</v>
       </c>
       <c r="G21">
-        <v>-5.810640886287268</v>
+        <v>-4.627196998545222</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.91245340644037</v>
       </c>
       <c r="E22">
-        <v>-26.96757650994745</v>
+        <v>-23.55698801038857</v>
       </c>
       <c r="F22">
-        <v>1.379107095047454</v>
+        <v>1.215328147802283</v>
       </c>
       <c r="G22">
-        <v>-5.693245630919172</v>
+        <v>-4.1331742193564</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.44117856620565</v>
       </c>
       <c r="E23">
-        <v>-26.7182296741371</v>
+        <v>-23.03234165422992</v>
       </c>
       <c r="F23">
-        <v>1.505228683035305</v>
+        <v>1.334666723354307</v>
       </c>
       <c r="G23">
-        <v>-5.761912966494735</v>
+        <v>-5.030636630688505</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.93397896916017</v>
       </c>
       <c r="E24">
-        <v>-27.18514704364597</v>
+        <v>-23.40534752976772</v>
       </c>
       <c r="F24">
-        <v>1.720178752114239</v>
+        <v>1.661771677952832</v>
       </c>
       <c r="G24">
-        <v>-5.300922810696762</v>
+        <v>-4.188566267319486</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.43011840180917</v>
       </c>
       <c r="E25">
-        <v>-27.98318190412169</v>
+        <v>-24.16803765061357</v>
       </c>
       <c r="F25">
-        <v>1.524999667683651</v>
+        <v>1.58734383475084</v>
       </c>
       <c r="G25">
-        <v>-5.594515231301488</v>
+        <v>-4.572228700411163</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.961671371160831</v>
       </c>
       <c r="E26">
-        <v>-27.21930532308583</v>
+        <v>-24.49981177031153</v>
       </c>
       <c r="F26">
-        <v>1.631412035553858</v>
+        <v>1.214324078251894</v>
       </c>
       <c r="G26">
-        <v>-5.536901807281551</v>
+        <v>-3.71114256346457</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.551347777012499</v>
       </c>
       <c r="E27">
-        <v>-27.27810302960142</v>
+        <v>-24.37075026109293</v>
       </c>
       <c r="F27">
-        <v>1.349376183896909</v>
+        <v>1.467701187663052</v>
       </c>
       <c r="G27">
-        <v>-4.918438931817065</v>
+        <v>-4.611150784316375</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.212911426827441</v>
       </c>
       <c r="E28">
-        <v>-27.82310940489855</v>
+        <v>-23.94369251979957</v>
       </c>
       <c r="F28">
-        <v>1.517389960759964</v>
+        <v>1.213259827876719</v>
       </c>
       <c r="G28">
-        <v>-5.835794411294651</v>
+        <v>-4.517919200839419</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.947687404553923</v>
       </c>
       <c r="E29">
-        <v>-28.9723817663572</v>
+        <v>-23.44901560462369</v>
       </c>
       <c r="F29">
-        <v>1.125984962288682</v>
+        <v>1.36968721226242</v>
       </c>
       <c r="G29">
-        <v>-5.140523568773534</v>
+        <v>-3.595981926335483</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.74793654991729</v>
       </c>
       <c r="E30">
-        <v>-28.17000409930813</v>
+        <v>-25.18212600599524</v>
       </c>
       <c r="F30">
-        <v>1.331988676651299</v>
+        <v>0.7096413467669749</v>
       </c>
       <c r="G30">
-        <v>-4.466456770431448</v>
+        <v>-2.848656065754866</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.599930886016345</v>
       </c>
       <c r="E31">
-        <v>-27.92917985158022</v>
+        <v>-24.27299862116335</v>
       </c>
       <c r="F31">
-        <v>1.3322452370096</v>
+        <v>0.8429925522588072</v>
       </c>
       <c r="G31">
-        <v>-4.368782434840791</v>
+        <v>-3.640803402391675</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.488126088607958</v>
       </c>
       <c r="E32">
-        <v>-28.73803323646026</v>
+        <v>-23.32540637811032</v>
       </c>
       <c r="F32">
-        <v>1.436913944666909</v>
+        <v>0.7299428728969932</v>
       </c>
       <c r="G32">
-        <v>-4.858203555730026</v>
+        <v>-4.102955559673933</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.396294463150619</v>
       </c>
       <c r="E33">
-        <v>-27.81898849355158</v>
+        <v>-24.42299979419343</v>
       </c>
       <c r="F33">
-        <v>1.295417739651971</v>
+        <v>0.8292380663832156</v>
       </c>
       <c r="G33">
-        <v>-4.858306182641743</v>
+        <v>-3.717661027631395</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.312903428653502</v>
       </c>
       <c r="E34">
-        <v>-27.14414171150651</v>
+        <v>-23.72105009521246</v>
       </c>
       <c r="F34">
-        <v>0.9019444212551252</v>
+        <v>1.036559424067478</v>
       </c>
       <c r="G34">
-        <v>-4.461616752853034</v>
+        <v>-3.53989797435469</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.227555927825305</v>
       </c>
       <c r="E35">
-        <v>-27.22674107740642</v>
+        <v>-23.07243223461983</v>
       </c>
       <c r="F35">
-        <v>1.017228709663624</v>
+        <v>0.9227733214549848</v>
       </c>
       <c r="G35">
-        <v>-4.584904779281032</v>
+        <v>-3.078950855648726</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.13290522373628</v>
       </c>
       <c r="E36">
-        <v>-27.09273900304545</v>
+        <v>-24.18135589267013</v>
       </c>
       <c r="F36">
-        <v>0.9335266846208187</v>
+        <v>0.8128641309234872</v>
       </c>
       <c r="G36">
-        <v>-3.967666805666077</v>
+        <v>-2.846550558791889</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.025614764447257</v>
       </c>
       <c r="E37">
-        <v>-26.27240140808195</v>
+        <v>-22.61998786803947</v>
       </c>
       <c r="F37">
-        <v>1.363602614135301</v>
+        <v>1.06979190899706</v>
       </c>
       <c r="G37">
-        <v>-3.929800785787893</v>
+        <v>-2.405870599877344</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.905711090346963</v>
       </c>
       <c r="E38">
-        <v>-26.43110630815477</v>
+        <v>-21.88680981230161</v>
       </c>
       <c r="F38">
-        <v>1.035727978461872</v>
+        <v>1.010847958530319</v>
       </c>
       <c r="G38">
-        <v>-4.106189962665801</v>
+        <v>-2.875329131164774</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.775564079061621</v>
       </c>
       <c r="E39">
-        <v>-26.21805971998991</v>
+        <v>-21.19350044172728</v>
       </c>
       <c r="F39">
-        <v>1.425126421538293</v>
+        <v>1.107900624440279</v>
       </c>
       <c r="G39">
-        <v>-3.770407949708603</v>
+        <v>-1.936713328233989</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.636857237989296</v>
       </c>
       <c r="E40">
-        <v>-25.20756244449633</v>
+        <v>-21.59292090615182</v>
       </c>
       <c r="F40">
-        <v>1.080789162873871</v>
+        <v>1.056778597489894</v>
       </c>
       <c r="G40">
-        <v>-3.944433397071471</v>
+        <v>-3.145539168625627</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.49408349180136</v>
       </c>
       <c r="E41">
-        <v>-26.27512302096056</v>
+        <v>-20.80767445627377</v>
       </c>
       <c r="F41">
-        <v>1.285530663621883</v>
+        <v>1.012221031559005</v>
       </c>
       <c r="G41">
-        <v>-3.700108515182179</v>
+        <v>-3.335144043296306</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.348794664404557</v>
       </c>
       <c r="E42">
-        <v>-25.37597186436758</v>
+        <v>-21.35014941460062</v>
       </c>
       <c r="F42">
-        <v>1.310968148035671</v>
+        <v>1.139055287208804</v>
       </c>
       <c r="G42">
-        <v>-4.325311661364622</v>
+        <v>-2.778601611598348</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.202515429501365</v>
       </c>
       <c r="E43">
-        <v>-24.36775241129985</v>
+        <v>-20.22419416580746</v>
       </c>
       <c r="F43">
-        <v>1.275792455947846</v>
+        <v>1.314189405867675</v>
       </c>
       <c r="G43">
-        <v>-4.180356114382094</v>
+        <v>-3.339500721225987</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.056205061007648</v>
       </c>
       <c r="E44">
-        <v>-24.49777395700808</v>
+        <v>-20.15839996695002</v>
       </c>
       <c r="F44">
-        <v>1.428027770775378</v>
+        <v>0.9992568149352176</v>
       </c>
       <c r="G44">
-        <v>-4.466241584971396</v>
+        <v>-3.258922042800126</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.910099502065672</v>
       </c>
       <c r="E45">
-        <v>-25.07951531345544</v>
+        <v>-20.1926261735</v>
       </c>
       <c r="F45">
-        <v>1.477868579640173</v>
+        <v>1.034628886556558</v>
       </c>
       <c r="G45">
-        <v>-4.33131368042732</v>
+        <v>-3.198507897253966</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.763536088233839</v>
       </c>
       <c r="E46">
-        <v>-24.45644257474007</v>
+        <v>-19.3515028828413</v>
       </c>
       <c r="F46">
-        <v>1.484323764951504</v>
+        <v>1.267726641720513</v>
       </c>
       <c r="G46">
-        <v>-4.760803995419129</v>
+        <v>-3.512811090752373</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.615776652135256</v>
       </c>
       <c r="E47">
-        <v>-24.13197741209049</v>
+        <v>-19.40142478030185</v>
       </c>
       <c r="F47">
-        <v>1.473266330249906</v>
+        <v>1.315071530062575</v>
       </c>
       <c r="G47">
-        <v>-4.812382294920973</v>
+        <v>-3.604910467654897</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.470261981915295</v>
       </c>
       <c r="E48">
-        <v>-22.5904259897174</v>
+        <v>-18.61255102274365</v>
       </c>
       <c r="F48">
-        <v>1.530108702966859</v>
+        <v>1.429845865166303</v>
       </c>
       <c r="G48">
-        <v>-6.016411154826208</v>
+        <v>-3.671038614801839</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.330731681287637</v>
       </c>
       <c r="E49">
-        <v>-23.33425954479531</v>
+        <v>-18.03130779843714</v>
       </c>
       <c r="F49">
-        <v>1.373991724940584</v>
+        <v>1.084952725725562</v>
       </c>
       <c r="G49">
-        <v>-5.061163171106124</v>
+        <v>-4.650566139506937</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.204034323127441</v>
       </c>
       <c r="E50">
-        <v>-22.76865766971129</v>
+        <v>-19.1015356460919</v>
       </c>
       <c r="F50">
-        <v>1.584214431861932</v>
+        <v>1.299080851434383</v>
       </c>
       <c r="G50">
-        <v>-5.272081337958631</v>
+        <v>-4.419039826672467</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.100056125705116</v>
       </c>
       <c r="E51">
-        <v>-21.86812080007196</v>
+        <v>-18.63671496004858</v>
       </c>
       <c r="F51">
-        <v>1.859224964077992</v>
+        <v>1.294735162402417</v>
       </c>
       <c r="G51">
-        <v>-5.915267367510395</v>
+        <v>-4.371768546917214</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.028202777177012</v>
       </c>
       <c r="E52">
-        <v>-21.61470286612872</v>
+        <v>-15.93153138513853</v>
       </c>
       <c r="F52">
-        <v>1.467645757956011</v>
+        <v>1.373047836214982</v>
       </c>
       <c r="G52">
-        <v>-5.504918626826653</v>
+        <v>-4.279751933653172</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.994068401104625</v>
       </c>
       <c r="E53">
-        <v>-22.47427968836867</v>
+        <v>-17.97957903984752</v>
       </c>
       <c r="F53">
-        <v>1.540222248942855</v>
+        <v>1.302051883731747</v>
       </c>
       <c r="G53">
-        <v>-5.76434290692056</v>
+        <v>-4.450284755472109</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.002427255916905</v>
       </c>
       <c r="E54">
-        <v>-20.50414442896165</v>
+        <v>-16.59364862674802</v>
       </c>
       <c r="F54">
-        <v>1.803093675317072</v>
+        <v>1.228203676894806</v>
       </c>
       <c r="G54">
-        <v>-6.392836735369039</v>
+        <v>-4.61539490369772</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.057616485053428</v>
       </c>
       <c r="E55">
-        <v>-21.49659573553467</v>
+        <v>-16.03815883412313</v>
       </c>
       <c r="F55">
-        <v>1.363176597244048</v>
+        <v>1.430390660001214</v>
       </c>
       <c r="G55">
-        <v>-6.201242222829258</v>
+        <v>-5.314681437957973</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.16081078551477</v>
       </c>
       <c r="E56">
-        <v>-20.85942585723343</v>
+        <v>-16.97400874407428</v>
       </c>
       <c r="F56">
-        <v>1.344072352786102</v>
+        <v>1.202839042953128</v>
       </c>
       <c r="G56">
-        <v>-6.583166619512817</v>
+        <v>-5.213981263744422</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.310477608945792</v>
       </c>
       <c r="E57">
-        <v>-20.64813178850953</v>
+        <v>-15.70850404026076</v>
       </c>
       <c r="F57">
-        <v>1.210436080229491</v>
+        <v>1.040143350554118</v>
       </c>
       <c r="G57">
-        <v>-6.468462837668149</v>
+        <v>-5.254167976045635</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.501838712637466</v>
       </c>
       <c r="E58">
-        <v>-20.62445692639743</v>
+        <v>-15.37548006173668</v>
       </c>
       <c r="F58">
-        <v>1.342990681645857</v>
+        <v>1.157145959880869</v>
       </c>
       <c r="G58">
-        <v>-6.488418806178876</v>
+        <v>-5.696393959727019</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.727997251927535</v>
       </c>
       <c r="E59">
-        <v>-20.32326812014728</v>
+        <v>-13.98493966209738</v>
       </c>
       <c r="F59">
-        <v>1.567959274345861</v>
+        <v>0.7595708431630344</v>
       </c>
       <c r="G59">
-        <v>-5.856945486745054</v>
+        <v>-5.530863372217921</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.979485475955214</v>
       </c>
       <c r="E60">
-        <v>-20.45055899602888</v>
+        <v>-15.0854313015454</v>
       </c>
       <c r="F60">
-        <v>1.262663533908853</v>
+        <v>0.9886269808307879</v>
       </c>
       <c r="G60">
-        <v>-6.583401668246106</v>
+        <v>-6.523272229616323</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.250823035917488</v>
       </c>
       <c r="E61">
-        <v>-20.38573841908309</v>
+        <v>-15.15063679878184</v>
       </c>
       <c r="F61">
-        <v>1.292720688477978</v>
+        <v>0.7295263582412326</v>
       </c>
       <c r="G61">
-        <v>-7.334650525290759</v>
+        <v>-5.47185951907149</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.537593105414072</v>
       </c>
       <c r="E62">
-        <v>-20.54642226229726</v>
+        <v>-15.51737526629302</v>
       </c>
       <c r="F62">
-        <v>1.501562403841062</v>
+        <v>1.228982860205202</v>
       </c>
       <c r="G62">
-        <v>-7.127585833445964</v>
+        <v>-5.515853358742866</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.835037742862515</v>
       </c>
       <c r="E63">
-        <v>-19.21232929116356</v>
+        <v>-14.6617744442318</v>
       </c>
       <c r="F63">
-        <v>0.8896295240566681</v>
+        <v>0.3650348580969283</v>
       </c>
       <c r="G63">
-        <v>-7.618529805283263</v>
+        <v>-6.464470319747788</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.137540605605265</v>
       </c>
       <c r="E64">
-        <v>-19.3582955938528</v>
+        <v>-13.97950549328817</v>
       </c>
       <c r="F64">
-        <v>0.8346654265554266</v>
+        <v>1.093146820132045</v>
       </c>
       <c r="G64">
-        <v>-8.672345971889607</v>
+        <v>-6.949554625980578</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.439196978204938</v>
       </c>
       <c r="E65">
-        <v>-19.03233603478069</v>
+        <v>-13.98064666873811</v>
       </c>
       <c r="F65">
-        <v>1.247019686876142</v>
+        <v>0.9237599702403037</v>
       </c>
       <c r="G65">
-        <v>-7.946737290046609</v>
+        <v>-8.06401336577529</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.734677606542952</v>
       </c>
       <c r="E66">
-        <v>-19.80303702614611</v>
+        <v>-13.89947830062462</v>
       </c>
       <c r="F66">
-        <v>1.244091414638494</v>
+        <v>0.9247228634368908</v>
       </c>
       <c r="G66">
-        <v>-8.037585280735289</v>
+        <v>-6.492841695019342</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.018389423938915</v>
       </c>
       <c r="E67">
-        <v>-19.01623730968342</v>
+        <v>-14.25150828455889</v>
       </c>
       <c r="F67">
-        <v>0.9150812618236954</v>
+        <v>0.602643007708055</v>
       </c>
       <c r="G67">
-        <v>-8.143065882707548</v>
+        <v>-7.216020436436515</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.292596236858071</v>
       </c>
       <c r="E68">
-        <v>-18.61975582488986</v>
+        <v>-13.53130430685301</v>
       </c>
       <c r="F68">
-        <v>0.9988149609848099</v>
+        <v>0.5598132649309105</v>
       </c>
       <c r="G68">
-        <v>-8.305693121778704</v>
+        <v>-6.597994552983213</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.557652690134598</v>
       </c>
       <c r="E69">
-        <v>-19.00630183771059</v>
+        <v>-14.61317033270748</v>
       </c>
       <c r="F69">
-        <v>0.8861263665717161</v>
+        <v>0.9561198332104779</v>
       </c>
       <c r="G69">
-        <v>-8.464288116383031</v>
+        <v>-8.030874804927185</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.810736634957429</v>
       </c>
       <c r="E70">
-        <v>-19.23215042189513</v>
+        <v>-13.11467111272531</v>
       </c>
       <c r="F70">
-        <v>0.7820547160445283</v>
+        <v>0.3901904428577685</v>
       </c>
       <c r="G70">
-        <v>-8.865102485913672</v>
+        <v>-7.852287425811202</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.04609233049513</v>
       </c>
       <c r="E71">
-        <v>-18.45765456931129</v>
+        <v>-13.83456262572467</v>
       </c>
       <c r="F71">
-        <v>0.9465479146575618</v>
+        <v>0.8110048601787613</v>
       </c>
       <c r="G71">
-        <v>-8.853826767806915</v>
+        <v>-7.838422861092734</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.25665650317871</v>
       </c>
       <c r="E72">
-        <v>-19.77685791790776</v>
+        <v>-14.31609790933029</v>
       </c>
       <c r="F72">
-        <v>0.895737877772518</v>
+        <v>0.7357344854297553</v>
       </c>
       <c r="G72">
-        <v>-9.334574259383258</v>
+        <v>-8.62018832691839</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.43605927970511</v>
       </c>
       <c r="E73">
-        <v>-18.95580029557705</v>
+        <v>-14.01672954963122</v>
       </c>
       <c r="F73">
-        <v>0.7503568421470077</v>
+        <v>0.8237552765039643</v>
       </c>
       <c r="G73">
-        <v>-9.468181256257164</v>
+        <v>-7.468707756358007</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.5795943401966</v>
       </c>
       <c r="E74">
-        <v>-19.48137046043326</v>
+        <v>-13.86464980703163</v>
       </c>
       <c r="F74">
-        <v>0.6618751926514057</v>
+        <v>0.542642725395716</v>
       </c>
       <c r="G74">
-        <v>-9.183682904248817</v>
+        <v>-8.064291451600589</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.68573726848989</v>
       </c>
       <c r="E75">
-        <v>-20.28711731214404</v>
+        <v>-15.77266798847544</v>
       </c>
       <c r="F75">
-        <v>0.7614950458502933</v>
+        <v>0.3693631263638243</v>
       </c>
       <c r="G75">
-        <v>-9.380974865661683</v>
+        <v>-7.846083463470608</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.74930194841462</v>
       </c>
       <c r="E76">
-        <v>-19.96204080550343</v>
+        <v>-14.36344763355449</v>
       </c>
       <c r="F76">
-        <v>0.6964585787268569</v>
+        <v>0.4937473889624385</v>
       </c>
       <c r="G76">
-        <v>-9.555490273764363</v>
+        <v>-8.050370607607954</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.76521442348763</v>
       </c>
       <c r="E77">
-        <v>-19.65959761195315</v>
+        <v>-15.59540540191919</v>
       </c>
       <c r="F77">
-        <v>0.4094237593478229</v>
+        <v>0.9885446281231851</v>
       </c>
       <c r="G77">
-        <v>-9.188582511646938</v>
+        <v>-8.412471457602358</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.73143467401168</v>
       </c>
       <c r="E78">
-        <v>-20.99311999536188</v>
+        <v>-15.64775456144786</v>
       </c>
       <c r="F78">
-        <v>0.5398300636898956</v>
+        <v>0.3314404963656691</v>
       </c>
       <c r="G78">
-        <v>-9.158459857785109</v>
+        <v>-8.801357931555005</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.64902195601126</v>
       </c>
       <c r="E79">
-        <v>-21.44379825707924</v>
+        <v>-15.98401639888742</v>
       </c>
       <c r="F79">
-        <v>0.684400241886701</v>
+        <v>0.4515756759931592</v>
       </c>
       <c r="G79">
-        <v>-9.694122678766885</v>
+        <v>-8.134670339219955</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.51890146014438</v>
       </c>
       <c r="E80">
-        <v>-21.97716192570265</v>
+        <v>-15.02738079324107</v>
       </c>
       <c r="F80">
-        <v>0.5795003131657384</v>
+        <v>0.272203560304572</v>
       </c>
       <c r="G80">
-        <v>-9.887163899707327</v>
+        <v>-8.119041253729057</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.34585842151742</v>
       </c>
       <c r="E81">
-        <v>-21.63472324971663</v>
+        <v>-17.3833329811536</v>
       </c>
       <c r="F81">
-        <v>0.3301869931335987</v>
+        <v>0.2732163402374955</v>
       </c>
       <c r="G81">
-        <v>-10.40259597689861</v>
+        <v>-7.915853210710748</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.13838864431016</v>
       </c>
       <c r="E82">
-        <v>-22.61634697493731</v>
+        <v>-17.71093637629049</v>
       </c>
       <c r="F82">
-        <v>0.4137163942316215</v>
+        <v>0.09447295579733771</v>
       </c>
       <c r="G82">
-        <v>-9.450661849263341</v>
+        <v>-8.135090778503443</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.906645801057923</v>
       </c>
       <c r="E83">
-        <v>-22.80441902894987</v>
+        <v>-18.22014516455699</v>
       </c>
       <c r="F83">
-        <v>0.2117843877775993</v>
+        <v>0.3815339063239765</v>
       </c>
       <c r="G83">
-        <v>-9.733875709602453</v>
+        <v>-8.27614650284071</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.66342811851759</v>
       </c>
       <c r="E84">
-        <v>-23.60387583026399</v>
+        <v>-19.72478952376757</v>
       </c>
       <c r="F84">
-        <v>0.491565042210963</v>
+        <v>0.3025267774674911</v>
       </c>
       <c r="G84">
-        <v>-9.745101769526121</v>
+        <v>-8.233920494487306</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.421708632799442</v>
       </c>
       <c r="E85">
-        <v>-25.21334530580412</v>
+        <v>-20.03518471767532</v>
       </c>
       <c r="F85">
-        <v>0.667988297485002</v>
+        <v>0.2594998633038744</v>
       </c>
       <c r="G85">
-        <v>-9.580531240223412</v>
+        <v>-8.67415021920851</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.192149058572427</v>
       </c>
       <c r="E86">
-        <v>-25.5683323832654</v>
+        <v>-21.69214430013389</v>
       </c>
       <c r="F86">
-        <v>0.6741409949664843</v>
+        <v>0.4479315686817331</v>
       </c>
       <c r="G86">
-        <v>-9.572135696735819</v>
+        <v>-8.027517911750365</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.979000299295821</v>
       </c>
       <c r="E87">
-        <v>-27.35167261833003</v>
+        <v>-21.93265608315527</v>
       </c>
       <c r="F87">
-        <v>0.5732858511535539</v>
+        <v>0.1306139166406236</v>
       </c>
       <c r="G87">
-        <v>-9.239786719502845</v>
+        <v>-7.86128879913248</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.788334593475788</v>
       </c>
       <c r="E88">
-        <v>-29.01962733567922</v>
+        <v>-23.74137841503289</v>
       </c>
       <c r="F88">
-        <v>0.7921508412554547</v>
+        <v>0.5131952976040349</v>
       </c>
       <c r="G88">
-        <v>-9.844726016439408</v>
+        <v>-7.127771223996163</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.622492748639042</v>
       </c>
       <c r="E89">
-        <v>-30.33861105328632</v>
+        <v>-26.80379971898604</v>
       </c>
       <c r="F89">
-        <v>0.8686470043830109</v>
+        <v>0.2282771011809857</v>
       </c>
       <c r="G89">
-        <v>-8.671309771135816</v>
+        <v>-7.677447584245672</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.483062670537816</v>
       </c>
       <c r="E90">
-        <v>-30.94909689849737</v>
+        <v>-27.49215493899598</v>
       </c>
       <c r="F90">
-        <v>0.9771625337089218</v>
+        <v>0.2541770277220824</v>
       </c>
       <c r="G90">
-        <v>-9.306600149576417</v>
+        <v>-8.10689486214547</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.37401919329735</v>
       </c>
       <c r="E91">
-        <v>-34.10606141854566</v>
+        <v>-28.18330875594266</v>
       </c>
       <c r="F91">
-        <v>0.9509157755723439</v>
+        <v>0.438851390815561</v>
       </c>
       <c r="G91">
-        <v>-9.406330333946961</v>
+        <v>-7.464887386805687</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.302035046304237</v>
       </c>
       <c r="E92">
-        <v>-35.49190579063901</v>
+        <v>-30.12881817369598</v>
       </c>
       <c r="F92">
-        <v>1.064804819069341</v>
+        <v>0.7084440650949027</v>
       </c>
       <c r="G92">
-        <v>-8.993809875389458</v>
+        <v>-8.291388254503515</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.274645155308169</v>
       </c>
       <c r="E93">
-        <v>-38.24420587336187</v>
+        <v>-33.85845351675426</v>
       </c>
       <c r="F93">
-        <v>0.9909059336431053</v>
+        <v>0.4831143874461781</v>
       </c>
       <c r="G93">
-        <v>-9.089448225473463</v>
+        <v>-7.036343887838111</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.296746250653253</v>
       </c>
       <c r="E94">
-        <v>-38.90490343836996</v>
+        <v>-34.74615669105585</v>
       </c>
       <c r="F94">
-        <v>1.387231506393658</v>
+        <v>0.6267897718007602</v>
       </c>
       <c r="G94">
-        <v>-8.910552965622326</v>
+        <v>-7.709328137788854</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.374419240814525</v>
       </c>
       <c r="E95">
-        <v>-42.59196659728214</v>
+        <v>-37.95663192421578</v>
       </c>
       <c r="F95">
-        <v>1.215655974926779</v>
+        <v>0.7137954073831726</v>
       </c>
       <c r="G95">
-        <v>-9.109728627447037</v>
+        <v>-7.201192502966119</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.508669330366617</v>
       </c>
       <c r="E96">
-        <v>-43.48404880594915</v>
+        <v>-39.82821173955687</v>
       </c>
       <c r="F96">
-        <v>1.649071940216924</v>
+        <v>1.192944048393462</v>
       </c>
       <c r="G96">
-        <v>-8.741347672564636</v>
+        <v>-7.369139788718886</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.691794931533641</v>
       </c>
       <c r="E97">
-        <v>-46.2072375935137</v>
+        <v>-42.86533019499216</v>
       </c>
       <c r="F97">
-        <v>1.516241773971271</v>
+        <v>1.342076883332648</v>
       </c>
       <c r="G97">
-        <v>-9.248771540096428</v>
+        <v>-6.646633088046185</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.920231976947596</v>
       </c>
       <c r="E98">
-        <v>-48.43199875730552</v>
+        <v>-44.08167152074141</v>
       </c>
       <c r="F98">
-        <v>1.803711320624093</v>
+        <v>1.093111978601905</v>
       </c>
       <c r="G98">
-        <v>-9.420873560500979</v>
+        <v>-7.857547882673104</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.172172453104112</v>
       </c>
       <c r="E99">
-        <v>-50.57827240959639</v>
+        <v>-47.82703878250233</v>
       </c>
       <c r="F99">
-        <v>1.793605693177674</v>
+        <v>1.059363205543891</v>
       </c>
       <c r="G99">
-        <v>-8.8278191220504</v>
+        <v>-8.040730298997596</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.43985505573988</v>
       </c>
       <c r="E100">
-        <v>-52.88752018083081</v>
+        <v>-49.53756341976063</v>
       </c>
       <c r="F100">
-        <v>1.854670225865188</v>
+        <v>1.459342387841362</v>
       </c>
       <c r="G100">
-        <v>-8.992108254982272</v>
+        <v>-7.907434493404381</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.679913342141166</v>
       </c>
       <c r="E101">
-        <v>-54.82891434782965</v>
+        <v>-52.20208469443732</v>
       </c>
       <c r="F101">
-        <v>1.873918587561439</v>
+        <v>1.464913865251878</v>
       </c>
       <c r="G101">
-        <v>-9.172301248684802</v>
+        <v>-7.651016188660131</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.908925681976951</v>
       </c>
       <c r="E102">
-        <v>-58.13653893387613</v>
+        <v>-54.89999101161705</v>
       </c>
       <c r="F102">
-        <v>2.15123816300221</v>
+        <v>1.742502670698274</v>
       </c>
       <c r="G102">
-        <v>-9.024948866731842</v>
+        <v>-7.63121912633529</v>
       </c>
     </row>
   </sheetData>
